--- a/artfynd/A 31700-2023 artfynd.xlsx
+++ b/artfynd/A 31700-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31700-2023 artfynd.xlsx
+++ b/artfynd/A 31700-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>697660</v>
       </c>
       <c r="B2" t="n">
-        <v>101402</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>102843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,6 +788,707 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>40911</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58799</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100069</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lövgroda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hyla arborea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Iglesjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>401302</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6153065</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Börringe</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1961-05-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1961-05-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långsmalt kärr i kullig naturbetesmark. Överordnad baslokal i Börringeområdet. Mycket mångstämmigt spel. (Vattnet finns avbildat som helplansch på sid. 192 i Djurens Värld 1962 av Hans Kauri. Fotot är taget ett par år tidigare i juni 1960).</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Boris Berglund</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Boris Berglund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6823822</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58799</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100069</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lövgroda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hyla arborea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>63-090 V Iglesjö, Klassiska baslokalen., Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>401343</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6153023</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Börringe</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Hallengren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Boris Berglund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>71959220</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58799</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100069</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lövgroda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hyla arborea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Boris baslokal, rockarp, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>401369</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6153011</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Börringe</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-05-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-05-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alexander Nordström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alexander Nordström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>94150180</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58799</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100069</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lövgroda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hyla arborea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svartesjö, vägen, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>401239</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6153152</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Börringe</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En ensam lövgroda hörd åt nordväst. Inget spel söder om vägen.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Pröjts</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Pröjts</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>22254</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58829</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100141</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Triturus cristatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>V Iglesjö. Klassiska baslokalen, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>401343</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6153023</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Börringe</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2001-03-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2001-03-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Hallengren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Boris Berglund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128082354</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57892</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103060</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Brun glada</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Milvus migrans</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Iglesjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>401473</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6153020</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Börringe</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Liljefors</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Liljefors, Petter Simonsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31700-2023 artfynd.xlsx
+++ b/artfynd/A 31700-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/697660</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/40911</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1034,6 +1049,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6823822</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1161,6 +1181,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71959220</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1273,6 +1298,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94150180</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1370,6 +1400,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/22254</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1489,8 +1524,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128082354</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>